--- a/utils/monday_sprint_sprint_2023-08.xlsx
+++ b/utils/monday_sprint_sprint_2023-08.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="122">
   <si>
     <t>Ticket</t>
   </si>
@@ -204,7 +204,28 @@
     <t>19585</t>
   </si>
   <si>
+    <t>Solicitação de serviço</t>
+  </si>
+  <si>
     <t>Alterações de vencimento de faturas de exportação para envio ao Benner</t>
+  </si>
+  <si>
+    <t>Prezados, Atualmente os vencimento que são alterados no sistema de faturas de exportação não estão atualizando as NFs de venda no Benner. Com o aumento das movimentações de exportação com parcelamentos de vencimentos nas faturas está inviável manter esse controle de forma manual, dessa forma solicit</t>
+  </si>
+  <si>
+    <t>Edson João Hammermeister</t>
+  </si>
+  <si>
+    <t>Sistemas</t>
+  </si>
+  <si>
+    <t>04/04/2023</t>
+  </si>
+  <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
+    <t>Abril</t>
   </si>
   <si>
     <t>19578</t>
@@ -1681,28 +1702,28 @@
         <v>16</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>17</v>
+        <v>67</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>20</v>
@@ -1711,12 +1732,12 @@
         <v>21</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>15</v>
@@ -1728,10 +1749,10 @@
         <v>17</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>19</v>
@@ -1760,7 +1781,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>15</v>
@@ -1772,10 +1793,10 @@
         <v>17</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>19</v>
@@ -1804,7 +1825,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>15</v>
@@ -1816,10 +1837,10 @@
         <v>17</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>19</v>
@@ -1837,7 +1858,7 @@
         <v>17</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>21</v>
@@ -1848,7 +1869,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>15</v>
@@ -1860,10 +1881,10 @@
         <v>17</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>19</v>
@@ -1892,25 +1913,25 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>17</v>
@@ -1928,7 +1949,7 @@
         <v>20</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>17</v>
@@ -1936,25 +1957,25 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>17</v>
@@ -1972,7 +1993,7 @@
         <v>20</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>17</v>
@@ -1980,25 +2001,25 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>17</v>
@@ -2016,7 +2037,7 @@
         <v>20</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>17</v>
@@ -2024,7 +2045,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>15</v>
@@ -2036,10 +2057,10 @@
         <v>17</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>19</v>
@@ -2060,7 +2081,7 @@
         <v>20</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>17</v>
@@ -2068,7 +2089,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>15</v>
@@ -2080,10 +2101,10 @@
         <v>17</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>25</v>
@@ -2112,7 +2133,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>15</v>
@@ -2124,10 +2145,10 @@
         <v>17</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>25</v>
@@ -2148,7 +2169,7 @@
         <v>20</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>17</v>
@@ -2167,23 +2188,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -2191,16 +2212,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2219,7 +2240,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -2232,7 +2253,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -2240,7 +2261,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -2271,12 +2292,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="B2">
         <v>30</v>
@@ -2300,25 +2321,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -2335,13 +2356,13 @@
         <v>22</v>
       </c>
       <c r="G10" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -2356,7 +2377,7 @@
         <v>21</v>
       </c>
       <c r="Q10">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
@@ -2373,19 +2394,19 @@
         <v>10</v>
       </c>
       <c r="J11" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="K11">
         <v>30</v>
       </c>
       <c r="M11" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="N11">
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="Q11">
         <v>4</v>
@@ -2393,7 +2414,7 @@
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -2405,16 +2426,16 @@
         <v>15</v>
       </c>
       <c r="M12" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="Q12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
@@ -2431,7 +2452,7 @@
         <v>2</v>
       </c>
       <c r="M13" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -2445,13 +2466,13 @@
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H14">
         <v>3</v>
       </c>
       <c r="M14" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -2459,7 +2480,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -2467,7 +2488,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -2475,7 +2496,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -2483,7 +2504,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -2494,7 +2515,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -2502,21 +2523,21 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>1126</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>18</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
@@ -2525,12 +2546,12 @@
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>15</v>
@@ -2539,12 +2560,12 @@
         <v>0</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>15</v>
@@ -2553,12 +2574,12 @@
         <v>0</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>15</v>
@@ -2567,12 +2588,12 @@
         <v>0</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>15</v>
@@ -2581,12 +2602,12 @@
         <v>0</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>15</v>
@@ -2595,12 +2616,12 @@
         <v>0</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>15</v>
@@ -2609,12 +2630,12 @@
         <v>0</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>15</v>
@@ -2623,12 +2644,12 @@
         <v>0</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>15</v>
@@ -2637,7 +2658,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/utils/monday_sprint_sprint_2023-08.xlsx
+++ b/utils/monday_sprint_sprint_2023-08.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="142">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>19033</t>
+    <t>4102836243</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>07/03/2023</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>25/04/2023</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,7 +102,7 @@
     <t>Março</t>
   </si>
   <si>
-    <t>19408</t>
+    <t>4209785897</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -117,16 +117,19 @@
     <t>27/03/2023</t>
   </si>
   <si>
+    <t>23/04/2023</t>
+  </si>
+  <si>
     <t>Semana 4</t>
   </si>
   <si>
-    <t>19406</t>
+    <t>4209794515</t>
   </si>
   <si>
     <t>Implantação - Projeto FATURA - Incluir data de liberação calculada no planilha do ERP</t>
   </si>
   <si>
-    <t>19098</t>
+    <t>4271460054</t>
   </si>
   <si>
     <t>Listagem CPC</t>
@@ -135,10 +138,13 @@
     <t>06/04/2023</t>
   </si>
   <si>
+    <t>13/04/2023</t>
+  </si>
+  <si>
     <t>Abril</t>
   </si>
   <si>
-    <t>19268</t>
+    <t>4271626401</t>
   </si>
   <si>
     <t>Botão para selecionar os contatos.</t>
@@ -147,7 +153,10 @@
     <t>Baixa</t>
   </si>
   <si>
-    <t>19350</t>
+    <t>19/04/2023</t>
+  </si>
+  <si>
+    <t>4271641706</t>
   </si>
   <si>
     <t>Análise</t>
@@ -156,76 +165,85 @@
     <t>Permitir informar a quantidade de peças na ajustagem.</t>
   </si>
   <si>
-    <t>19487</t>
+    <t>4271778649</t>
   </si>
   <si>
     <t>Alterar relatório Saldo Físico do estoque no Depósito Fabril</t>
   </si>
   <si>
-    <t>19494</t>
+    <t>22/04/2023</t>
+  </si>
+  <si>
+    <t>4271868138</t>
   </si>
   <si>
     <t>Melhorias SIC WEB 1</t>
   </si>
   <si>
-    <t>19498</t>
+    <t>18/04/2023</t>
+  </si>
+  <si>
+    <t>4271894519</t>
   </si>
   <si>
     <t>Melhorias SIC WEB 2</t>
   </si>
   <si>
-    <t>19496</t>
+    <t>4271901947</t>
   </si>
   <si>
     <t>Melhorias SIC WEB 3</t>
   </si>
   <si>
-    <t>19497</t>
+    <t>4271911076</t>
   </si>
   <si>
     <t>Melhorias SIC WEB 4</t>
   </si>
   <si>
+    <t>4271914165</t>
+  </si>
+  <si>
     <t>Melhorias SIC WEB 5</t>
   </si>
   <si>
-    <t>19499</t>
+    <t>4271921423</t>
   </si>
   <si>
     <t>Melhorias SIC WEB 6</t>
   </si>
   <si>
-    <t>19630</t>
+    <t>4271926673</t>
   </si>
   <si>
     <t>Melhorias SIC WEB 7</t>
   </si>
   <si>
-    <t>19488</t>
+    <t>4271952903</t>
   </si>
   <si>
     <t>Relatório horas trabalhadas moldagem</t>
   </si>
   <si>
-    <t>19631</t>
+    <t>4272033912</t>
   </si>
   <si>
     <t>Melhorias SIC WEB 8</t>
   </si>
   <si>
-    <t>19543</t>
+    <t>4272056106</t>
   </si>
   <si>
     <t>Alterações na tela de movimentação setorial</t>
   </si>
   <si>
-    <t>19567</t>
+    <t>4272075379</t>
   </si>
   <si>
     <t>Blocos de Prova - Engenharia</t>
   </si>
   <si>
-    <t>19443</t>
+    <t>4272549719</t>
   </si>
   <si>
     <t>Lançamentos Fiscais x baixas indevidas</t>
@@ -255,28 +273,31 @@
     <t>19/05/2026</t>
   </si>
   <si>
-    <t>19578</t>
+    <t>4272931614</t>
   </si>
   <si>
     <t>Blocos de Prova - Programação Moldagem</t>
   </si>
   <si>
+    <t>4273061783</t>
+  </si>
+  <si>
     <t>Blocos de Prova - Programação Aciaria</t>
   </si>
   <si>
-    <t>18941</t>
+    <t>4273295336</t>
   </si>
   <si>
     <t>Produtivo em Horas</t>
   </si>
   <si>
+    <t>10/04/2023</t>
+  </si>
+  <si>
     <t>A fazer</t>
   </si>
   <si>
-    <t>Aberto</t>
-  </si>
-  <si>
-    <t>9107</t>
+    <t>4273390001</t>
   </si>
   <si>
     <t>Sugestões de Alteração de fluxo pelo Usuario</t>
@@ -297,6 +318,9 @@
     <t>11/04/2023</t>
   </si>
   <si>
+    <t>24/04/2023</t>
+  </si>
+  <si>
     <t>Semana 2</t>
   </si>
   <si>
@@ -306,7 +330,7 @@
     <t>4291581142</t>
   </si>
   <si>
-    <t>19465</t>
+    <t>4291665638</t>
   </si>
   <si>
     <t>CBENEF-Código de Benefício Fiscal</t>
@@ -318,10 +342,7 @@
     <t>Inclusão das informações do projeto no fluxo de caixa</t>
   </si>
   <si>
-    <t>25/04/2023</t>
-  </si>
-  <si>
-    <t>19410</t>
+    <t>4341184214</t>
   </si>
   <si>
     <t>Simulações projeto FATURA</t>
@@ -339,7 +360,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2023-08</t>
+    <t>Mar/2023</t>
   </si>
   <si>
     <t>Base</t>
@@ -978,7 +999,7 @@
         <v>33</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -987,7 +1008,7 @@
         <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O3" s="2" t="s">
         <v>28</v>
@@ -995,7 +1016,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -1007,10 +1028,10 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>32</v>
@@ -1025,7 +1046,7 @@
         <v>33</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
@@ -1034,7 +1055,7 @@
         <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>28</v>
@@ -1042,7 +1063,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
@@ -1054,10 +1075,10 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>20</v>
@@ -1069,10 +1090,10 @@
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
@@ -1084,12 +1105,12 @@
         <v>27</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1101,13 +1122,13 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>21</v>
@@ -1116,10 +1137,10 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -1131,27 +1152,27 @@
         <v>27</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1163,10 +1184,10 @@
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1178,12 +1199,12 @@
         <v>27</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1195,10 +1216,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1210,10 +1231,10 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1225,12 +1246,12 @@
         <v>27</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1242,10 +1263,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>32</v>
@@ -1257,10 +1278,10 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
@@ -1272,12 +1293,12 @@
         <v>27</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1289,10 +1310,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>32</v>
@@ -1304,10 +1325,10 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1319,12 +1340,12 @@
         <v>27</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1336,10 +1357,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>32</v>
@@ -1351,10 +1372,10 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1366,12 +1387,12 @@
         <v>27</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1383,10 +1404,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>32</v>
@@ -1398,10 +1419,10 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1413,12 +1434,12 @@
         <v>27</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1430,10 +1451,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>32</v>
@@ -1445,10 +1466,10 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1460,12 +1481,12 @@
         <v>27</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1477,10 +1498,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>32</v>
@@ -1492,10 +1513,10 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1507,12 +1528,12 @@
         <v>27</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1524,10 +1545,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1539,10 +1560,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1554,12 +1575,12 @@
         <v>27</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1571,13 +1592,13 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>21</v>
@@ -1586,10 +1607,10 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1601,12 +1622,12 @@
         <v>27</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1618,10 +1639,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1633,10 +1654,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1648,12 +1669,12 @@
         <v>27</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1665,10 +1686,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -1680,10 +1701,10 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1695,12 +1716,12 @@
         <v>27</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1712,10 +1733,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1727,10 +1748,10 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1742,12 +1763,12 @@
         <v>27</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1759,10 +1780,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -1774,10 +1795,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1789,42 +1810,42 @@
         <v>27</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1836,12 +1857,12 @@
         <v>27</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1853,10 +1874,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -1868,10 +1889,10 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -1883,12 +1904,12 @@
         <v>27</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -1900,10 +1921,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -1915,10 +1936,10 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -1930,12 +1951,12 @@
         <v>27</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -1947,10 +1968,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -1962,27 +1983,27 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>86</v>
+        <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -1994,10 +2015,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2009,10 +2030,10 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2024,30 +2045,30 @@
         <v>27</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>21</v>
@@ -2056,10 +2077,10 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2068,33 +2089,33 @@
         <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>21</v>
@@ -2103,10 +2124,10 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2115,33 +2136,33 @@
         <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>21</v>
@@ -2150,10 +2171,10 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>101</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2162,15 +2183,15 @@
         <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2182,10 +2203,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2197,10 +2218,10 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>25</v>
@@ -2209,15 +2230,15 @@
         <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2229,10 +2250,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>32</v>
@@ -2244,11 +2265,11 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K30" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="K30" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
       </c>
@@ -2256,15 +2277,15 @@
         <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2276,10 +2297,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>32</v>
@@ -2291,10 +2312,10 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="L31" s="2" t="s">
         <v>25</v>
@@ -2303,10 +2324,10 @@
         <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -2322,23 +2343,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="B2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="E2" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -2346,16 +2367,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2366,7 +2387,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>1139</v>
+        <v>54.24</v>
       </c>
       <c r="J5" s="4">
         <v>2</v>
@@ -2374,7 +2395,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -2387,7 +2408,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -2395,7 +2416,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -2426,12 +2447,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="B2">
         <v>30</v>
@@ -2445,7 +2466,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>1139</v>
+        <v>54.24</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -2455,25 +2476,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -2490,13 +2511,13 @@
         <v>22</v>
       </c>
       <c r="G10" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -2508,15 +2529,15 @@
         <v>29</v>
       </c>
       <c r="P10" t="s">
-        <v>27</v>
+        <v>102</v>
       </c>
       <c r="Q10">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -2537,24 +2558,24 @@
         <v>26</v>
       </c>
       <c r="K11">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M11" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="N11">
         <v>1</v>
       </c>
       <c r="P11" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="Q11">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -2566,59 +2587,53 @@
         <v>15</v>
       </c>
       <c r="J12" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>105</v>
+        <v>35</v>
       </c>
       <c r="Q12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="4:17" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H13">
         <v>2</v>
       </c>
       <c r="M13" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="N13">
         <v>0</v>
       </c>
-      <c r="P13" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q13">
-        <v>3</v>
-      </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="H14">
         <v>3</v>
       </c>
       <c r="M14" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -2626,7 +2641,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -2634,7 +2649,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -2642,7 +2657,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -2650,10 +2665,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -2661,7 +2676,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -2669,142 +2684,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>73</v>
+        <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>1124</v>
+        <v>1184</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>15</v>
+        <v>78</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>1156</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="2">
         <v>35</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F24" s="2">
-        <v>0</v>
-      </c>
       <c r="G24" s="2" t="s">
-        <v>36</v>
+        <v>98</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>37</v>
+        <v>103</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>38</v>
+        <v>98</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>41</v>
+        <v>104</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>42</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>46</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
